--- a/data/trans_orig/P33B1_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P33B1_2023-Habitat-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según la frecuencia con la que tiene dificultad para dormirse por la noche en 2023</t>
+          <t>Población según la frecuencia con la que tiene dificultad para dormirse por la noche en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>33252</t>
+          <t>32708</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>59294</t>
+          <t>59449</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>67055</t>
+          <t>68609</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>93005</t>
+          <t>93267</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>107713</t>
+          <t>106890</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>144397</t>
+          <t>142496</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,88%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>36430</t>
+          <t>34966</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>60972</t>
+          <t>60227</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,61%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>69634</t>
+          <t>68950</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>95501</t>
+          <t>94405</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>111043</t>
+          <t>111212</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>147150</t>
+          <t>145780</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,13%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>117619</t>
+          <t>117023</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>158788</t>
+          <t>156264</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>158717</t>
+          <t>158058</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>191886</t>
+          <t>193278</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>284186</t>
+          <t>281868</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>340141</t>
+          <t>336521</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,98%</t>
+          <t>25,7%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>383536</t>
+          <t>380873</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>433203</t>
+          <t>432265</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>60,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,28%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>318394</t>
+          <t>317550</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>358085</t>
+          <t>360423</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>47,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,06%</t>
+          <t>53,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>714034</t>
+          <t>712099</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>779024</t>
+          <t>784591</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>59,93%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>27841</t>
+          <t>28375</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>78238</t>
+          <t>79270</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,38%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>94246</t>
+          <t>93087</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>125536</t>
+          <t>125676</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>109776</t>
+          <t>110775</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>196647</t>
+          <t>196457</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,13%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27550</t>
+          <t>27751</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>74969</t>
+          <t>73258</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>75255</t>
+          <t>76069</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>103142</t>
+          <t>104012</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>93965</t>
+          <t>95465</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>168515</t>
+          <t>169709</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,89%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>88604</t>
+          <t>72202</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>208496</t>
+          <t>211287</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>224595</t>
+          <t>223400</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>267221</t>
+          <t>267454</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>269989</t>
+          <t>260413</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>467159</t>
+          <t>466050</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,72%</t>
+          <t>21,67%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>842256</t>
+          <t>842767</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1044888</t>
+          <t>1063087</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>70,61%</t>
+          <t>70,65%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>89,12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>491893</t>
+          <t>491856</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>543069</t>
+          <t>542767</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1693,7 +1693,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>56,68%</t>
+          <t>56,65%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1333836</t>
+          <t>1337492</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1668422</t>
+          <t>1684524</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>62,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>77,57%</t>
+          <t>78,31%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28791</t>
+          <t>28932</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>56397</t>
+          <t>57222</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>26868</t>
+          <t>25920</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>74950</t>
+          <t>74797</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>59223</t>
+          <t>63169</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>115309</t>
+          <t>118119</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24811</t>
+          <t>24890</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>52809</t>
+          <t>53560</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>31632</t>
+          <t>30721</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>88074</t>
+          <t>85754</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>64582</t>
+          <t>63676</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>121748</t>
+          <t>123495</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,54%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>129399</t>
+          <t>130726</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>181561</t>
+          <t>177887</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>82305</t>
+          <t>75851</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>205222</t>
+          <t>203598</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,82%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>201817</t>
+          <t>199765</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>359844</t>
+          <t>362379</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,12%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>445539</t>
+          <t>444879</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>504071</t>
+          <t>501281</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,23%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,53%</t>
+          <t>71,14%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>575266</t>
+          <t>580012</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>782715</t>
+          <t>801708</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>62,14%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>83,86%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1057502</t>
+          <t>1056636</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1302603</t>
+          <t>1302244</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,56%</t>
+          <t>64,51%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,5%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>59113</t>
+          <t>57512</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>91579</t>
+          <t>92266</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>100117</t>
+          <t>96814</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>141680</t>
+          <t>143864</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>170828</t>
+          <t>167427</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>222776</t>
+          <t>221610</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>8,29%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>10,98%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>51308</t>
+          <t>51412</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>84636</t>
+          <t>82661</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>85511</t>
+          <t>87368</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>127819</t>
+          <t>128893</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,0%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,8%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>150994</t>
+          <t>148618</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>200987</t>
+          <t>198620</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>151853</t>
+          <t>151408</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>199911</t>
+          <t>198066</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,34%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>182822</t>
+          <t>189222</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>261425</t>
+          <t>263939</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>24,17%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>357150</t>
+          <t>363258</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>447161</t>
+          <t>446224</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,1%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>583953</t>
+          <t>586392</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>643446</t>
+          <t>644905</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>63,27%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>69,42%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>584799</t>
+          <t>579235</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>726603</t>
+          <t>721527</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>53,04%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>66,54%</t>
+          <t>66,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1190241</t>
+          <t>1189725</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1327331</t>
+          <t>1332332</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>58,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>65,75%</t>
+          <t>65,99%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>172956</t>
+          <t>168068</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>250616</t>
+          <t>249579</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>295852</t>
+          <t>293250</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>400890</t>
+          <t>403360</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>504513</t>
+          <t>503996</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>631272</t>
+          <t>634570</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>8,92%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>156975</t>
+          <t>159525</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>235374</t>
+          <t>235524</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,7 +3134,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>279624</t>
+          <t>279869</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>377380</t>
+          <t>381421</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,43%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>472990</t>
+          <t>467339</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>595723</t>
+          <t>594319</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,35%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>476973</t>
+          <t>473725</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>687423</t>
+          <t>687018</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,87%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>638320</t>
+          <t>665901</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>874498</t>
+          <t>877771</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1242481</t>
+          <t>1231754</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1527666</t>
+          <t>1532344</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,46%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,53%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2323366</t>
+          <t>2317871</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2677144</t>
+          <t>2670482</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>67,17%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>77,4%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2027298</t>
+          <t>2020954</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2480848</t>
+          <t>2453799</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>55,24%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>67,07%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>4407633</t>
+          <t>4389629</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>4928401</t>
+          <t>4883507</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>61,68%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>69,25%</t>
+          <t>68,62%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P33B1_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P33B1_2023-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>44483</t>
+          <t>49068</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32708</t>
+          <t>36511</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>59449</t>
+          <t>64248</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,16%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>79873</t>
+          <t>87885</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>68609</t>
+          <t>74776</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>93267</t>
+          <t>103405</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>11,84%</t>
+          <t>12,0%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>124356</t>
+          <t>136953</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>106890</t>
+          <t>118357</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>142496</t>
+          <t>156056</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,98%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>47311</t>
+          <t>51154</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>34966</t>
+          <t>38785</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>60227</t>
+          <t>66253</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>81512</t>
+          <t>89815</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>68950</t>
+          <t>77308</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>94405</t>
+          <t>104731</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,27%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>128823</t>
+          <t>140969</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>111212</t>
+          <t>124674</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>145780</t>
+          <t>161311</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,35%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>135822</t>
+          <t>147800</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>117023</t>
+          <t>127625</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>156264</t>
+          <t>170698</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,75%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>174445</t>
+          <t>185304</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>158058</t>
+          <t>168659</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>193278</t>
+          <t>203456</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>310267</t>
+          <t>333104</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>281868</t>
+          <t>305344</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>336521</t>
+          <t>362196</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>23,7%</t>
+          <t>23,43%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>25,47%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>406795</t>
+          <t>441606</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>380873</t>
+          <t>417508</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>432265</t>
+          <t>468367</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>64,04%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>60,54%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,14%</t>
+          <t>67,92%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>339037</t>
+          <t>369179</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>317550</t>
+          <t>347264</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>360423</t>
+          <t>393579</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>50,24%</t>
+          <t>50,42%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,41%</t>
+          <t>53,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>745833</t>
+          <t>810785</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>712099</t>
+          <t>776812</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>784591</t>
+          <t>844717</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>56,97%</t>
+          <t>57,02%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>59,93%</t>
+          <t>59,41%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>634412</t>
+          <t>689628</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>634412</t>
+          <t>689628</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>634412</t>
+          <t>689628</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>674867</t>
+          <t>732183</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>674867</t>
+          <t>732183</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>674867</t>
+          <t>732183</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1309279</t>
+          <t>1421811</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1309279</t>
+          <t>1421811</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1309279</t>
+          <t>1421811</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>57290</t>
+          <t>63824</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>28375</t>
+          <t>50037</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>79270</t>
+          <t>80073</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>4,77%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>108141</t>
+          <t>120607</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>93087</t>
+          <t>103402</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>125676</t>
+          <t>141310</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>165431</t>
+          <t>184431</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>110775</t>
+          <t>159632</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>196457</t>
+          <t>208572</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,84%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>52279</t>
+          <t>55123</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>27751</t>
+          <t>42478</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>73258</t>
+          <t>72553</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>6,92%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>89089</t>
+          <t>97840</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>76069</t>
+          <t>83950</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>104012</t>
+          <t>112455</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>7,94%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>141367</t>
+          <t>152963</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>95465</t>
+          <t>133097</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>169709</t>
+          <t>174984</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>8,25%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>158846</t>
+          <t>185031</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>72202</t>
+          <t>162175</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>211287</t>
+          <t>210577</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>13,32%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>243855</t>
+          <t>270081</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>223400</t>
+          <t>248818</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>267454</t>
+          <t>295001</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>23,32%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>402701</t>
+          <t>455112</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>260413</t>
+          <t>420377</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>466050</t>
+          <t>491956</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>23,21%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>924449</t>
+          <t>744939</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>842767</t>
+          <t>716565</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1063087</t>
+          <t>774427</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>77,5%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>89,12%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>517022</t>
+          <t>582310</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>491856</t>
+          <t>552735</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>542767</t>
+          <t>612340</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>54,38%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>51,34%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>56,65%</t>
+          <t>57,18%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1441472</t>
+          <t>1327248</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1337492</t>
+          <t>1283375</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1684524</t>
+          <t>1371581</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>62,61%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>62,18%</t>
+          <t>60,54%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>78,31%</t>
+          <t>64,7%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>40537</t>
+          <t>44014</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>28932</t>
+          <t>32040</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>57222</t>
+          <t>62008</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>53570</t>
+          <t>63219</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>25920</t>
+          <t>50754</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>74797</t>
+          <t>78298</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>94107</t>
+          <t>107233</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>63169</t>
+          <t>90027</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>118119</t>
+          <t>131965</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>5,57%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>35699</t>
+          <t>41046</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>24890</t>
+          <t>30099</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>53560</t>
+          <t>59403</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>61953</t>
+          <t>75568</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>30721</t>
+          <t>61968</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>85754</t>
+          <t>94752</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>11,67%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>97651</t>
+          <t>116613</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>63676</t>
+          <t>97501</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>123495</t>
+          <t>138174</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>152549</t>
+          <t>174099</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>130726</t>
+          <t>150634</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>177887</t>
+          <t>202188</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>150885</t>
+          <t>181482</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>75851</t>
+          <t>159787</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>203598</t>
+          <t>205367</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>303433</t>
+          <t>355581</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>199765</t>
+          <t>324132</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>362379</t>
+          <t>394347</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>22,01%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>12,2%</t>
+          <t>20,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>22,12%</t>
+          <t>24,41%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>475896</t>
+          <t>543914</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>444879</t>
+          <t>513757</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>501281</t>
+          <t>572379</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>63,13%</t>
+          <t>63,97%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>666959</t>
+          <t>491991</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>580012</t>
+          <t>464393</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>801708</t>
+          <t>517073</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>71,46%</t>
+          <t>60,57%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>57,17%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>63,66%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1142854</t>
+          <t>1035905</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1056636</t>
+          <t>996723</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1302244</t>
+          <t>1076768</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>64,13%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,51%</t>
+          <t>61,7%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>66,66%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>704680</t>
+          <t>803073</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>933366</t>
+          <t>812259</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1638046</t>
+          <t>1615332</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>73054</t>
+          <t>78374</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>57512</t>
+          <t>62127</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>92266</t>
+          <t>96897</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>122727</t>
+          <t>140402</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>96814</t>
+          <t>122505</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>143864</t>
+          <t>160534</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>14,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>195781</t>
+          <t>218776</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>167427</t>
+          <t>194551</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>221610</t>
+          <t>245150</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>11,63%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>65590</t>
+          <t>66745</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>51412</t>
+          <t>52567</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>82661</t>
+          <t>84961</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>6,74%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>109196</t>
+          <t>118657</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>87368</t>
+          <t>103211</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>128893</t>
+          <t>135267</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,0%</t>
+          <t>9,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>11,8%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>174787</t>
+          <t>185402</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>148618</t>
+          <t>163283</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>198620</t>
+          <t>210443</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,8%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,75%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>9,98%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>173845</t>
+          <t>183800</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>151408</t>
+          <t>159286</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>198066</t>
+          <t>210359</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,56%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,34%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,25%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>234983</t>
+          <t>257571</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>189222</t>
+          <t>233845</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>263939</t>
+          <t>281415</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>21,52%</t>
+          <t>23,04%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>20,92%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>408827</t>
+          <t>441372</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>363258</t>
+          <t>406155</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>446224</t>
+          <t>477338</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>17,99%</t>
+          <t>19,27%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>22,65%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>614342</t>
+          <t>661143</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>586392</t>
+          <t>628212</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>644905</t>
+          <t>689131</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>66,78%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>63,27%</t>
+          <t>63,45%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,6%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>625121</t>
+          <t>601120</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>579235</t>
+          <t>573758</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>721527</t>
+          <t>631342</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>57,24%</t>
+          <t>53,78%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>51,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1239463</t>
+          <t>1262263</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1189725</t>
+          <t>1218237</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1332332</t>
+          <t>1301349</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>59,88%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>57,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>65,99%</t>
+          <t>61,74%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1092027</t>
+          <t>1117750</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1092027</t>
+          <t>1117750</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1092027</t>
+          <t>1117750</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2018858</t>
+          <t>2107812</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2018858</t>
+          <t>2107812</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2018858</t>
+          <t>2107812</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>215365</t>
+          <t>235280</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>168068</t>
+          <t>204381</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>249579</t>
+          <t>265608</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>6,23%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>364310</t>
+          <t>412114</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>293250</t>
+          <t>378483</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>403360</t>
+          <t>446216</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,95%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>579675</t>
+          <t>647393</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>503996</t>
+          <t>604744</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>634570</t>
+          <t>696240</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>8,32%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>8,92%</t>
+          <t>9,58%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>200879</t>
+          <t>214067</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>159525</t>
+          <t>187792</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>235524</t>
+          <t>246156</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>341750</t>
+          <t>381879</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>279869</t>
+          <t>351845</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>381421</t>
+          <t>411565</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>10,23%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>11,02%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>542628</t>
+          <t>595947</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>467339</t>
+          <t>551476</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>594319</t>
+          <t>640959</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>8,2%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>621062</t>
+          <t>690730</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>473725</t>
+          <t>646410</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>687018</t>
+          <t>746665</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>13,7%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>804167</t>
+          <t>894439</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>665901</t>
+          <t>852398</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>877771</t>
+          <t>938218</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>23,99%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1425229</t>
+          <t>1585169</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1231754</t>
+          <t>1519010</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1532344</t>
+          <t>1652378</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>20,03%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>22,75%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>2421482</t>
+          <t>2391603</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>2317871</t>
+          <t>2335211</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>2670482</t>
+          <t>2447533</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>70,01%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>66,12%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>2148139</t>
+          <t>2044599</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2020954</t>
+          <t>1994367</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>2453799</t>
+          <t>2098085</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>54,77%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>53,42%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>4569622</t>
+          <t>4436201</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>4389629</t>
+          <t>4357154</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>4883507</t>
+          <t>4515442</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>64,21%</t>
+          <t>61,07%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>59,98%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>68,62%</t>
+          <t>62,16%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3458787</t>
+          <t>3531680</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3458787</t>
+          <t>3531680</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3458787</t>
+          <t>3531680</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3658366</t>
+          <t>3733030</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3658366</t>
+          <t>3733030</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3658366</t>
+          <t>3733030</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>7117154</t>
+          <t>7264710</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7117154</t>
+          <t>7264710</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7117154</t>
+          <t>7264710</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
